--- a/results/tables/tableA1_temporal_placebo.xlsx
+++ b/results/tables/tableA1_temporal_placebo.xlsx
@@ -14,17 +14,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>specification</t>
+  </si>
   <si>
     <t>specification_id</t>
   </si>
   <si>
-    <t>outcome</t>
-  </si>
-  <si>
-    <t>key_predictor</t>
-  </si>
-  <si>
     <t>coefficient</t>
   </si>
   <si>
@@ -34,43 +31,34 @@
     <t>p_value</t>
   </si>
   <si>
-    <t>sig</t>
-  </si>
-  <si>
-    <t>ci_lower</t>
-  </si>
-  <si>
-    <t>ci_upper</t>
-  </si>
-  <si>
-    <t>ci_level</t>
-  </si>
-  <si>
     <t>n</t>
   </si>
   <si>
     <t>n_entities</t>
   </si>
   <si>
-    <t>year_range</t>
-  </si>
-  <si>
-    <t>fe_structure</t>
-  </si>
-  <si>
-    <t>cluster_level</t>
-  </si>
-  <si>
-    <t>controls</t>
-  </si>
-  <si>
-    <t>sample_definition</t>
-  </si>
-  <si>
-    <t>timing_window</t>
-  </si>
-  <si>
-    <t>transformation</t>
+    <t>2-13 mo pre-allocation (reference)</t>
+  </si>
+  <si>
+    <t>Future-news raw placebo (t+1)</t>
+  </si>
+  <si>
+    <t>Future-news innovation placebo (AR(2) residual of t+1)</t>
+  </si>
+  <si>
+    <t>14-25 mo pre-allocation window</t>
+  </si>
+  <si>
+    <t>14-25 mo future-media placebo (t+13..t+24)</t>
+  </si>
+  <si>
+    <t>26-37 mo pre-allocation window</t>
+  </si>
+  <si>
+    <t>26-37 mo future-media placebo (t+25..t+36)</t>
+  </si>
+  <si>
+    <t>H1_preferred__devrel_media_m1_13</t>
   </si>
   <si>
     <t>placebo_future_news_raw__future_news_t1</t>
@@ -79,40 +67,16 @@
     <t>placebo_future_news_ar2_innovation__innovation_ar2</t>
   </si>
   <si>
-    <t>ln_devrel_commitment_musd</t>
-  </si>
-  <si>
-    <t>future_news_t1</t>
-  </si>
-  <si>
-    <t>innovation_ar2</t>
-  </si>
-  <si>
-    <t>country + year</t>
-  </si>
-  <si>
-    <t>country</t>
-  </si>
-  <si>
-    <t>ln_gdppc;ln_population;log_bilateral_trade;ln_conflict_deaths;ln_disaster_affected</t>
-  </si>
-  <si>
-    <t>Devrel-ODA panel, complete cases (raw future-news placebo, its own maximal sample)</t>
-  </si>
-  <si>
-    <t>Devrel-ODA panel, complete cases (AR(2)-innovation placebo, restricted to the AR(2) first-stage sample)</t>
-  </si>
-  <si>
-    <t>future news, Jan-Dec of calendar year t+1 (raw, unresidualized)</t>
-  </si>
-  <si>
-    <t>AR(2) innovation (residual) of Jan-Dec year t+1 future news, net of news_t and news_t-1</t>
-  </si>
-  <si>
-    <t>ln(x+1)</t>
-  </si>
-  <si>
-    <t>AR(2) residual (unitless)</t>
+    <t>placebo_future_news_m14_25_pre__devrel_media_m14_25</t>
+  </si>
+  <si>
+    <t>placebo_future_news_m14_25_future__future_m14_25</t>
+  </si>
+  <si>
+    <t>placebo_future_news_m26_37_pre__devrel_media_m26_37</t>
+  </si>
+  <si>
+    <t>placebo_future_news_m26_37_future__future_m26_37</t>
   </si>
 </sst>
 </file>
@@ -470,10 +434,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -495,147 +459,166 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>0.0842931125485394</v>
+      </c>
+      <c r="D2">
+        <v>0.0399627426453581</v>
+      </c>
+      <c r="E2">
+        <v>0.0350401845896148</v>
+      </c>
+      <c r="F2">
+        <v>2214</v>
+      </c>
+      <c r="G2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>0.0480744591291271</v>
+      </c>
+      <c r="D3">
+        <v>0.0328988971704961</v>
+      </c>
+      <c r="E3">
+        <v>0.1441026766242277</v>
+      </c>
+      <c r="F3">
+        <v>2080</v>
+      </c>
+      <c r="G3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>0.0476889951911409</v>
+      </c>
+      <c r="D4">
+        <v>0.0326653359814922</v>
+      </c>
+      <c r="E4">
+        <v>0.1444865908404664</v>
+      </c>
+      <c r="F4">
+        <v>1941</v>
+      </c>
+      <c r="G4">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>0.0630506819103047</v>
+      </c>
+      <c r="D5">
+        <v>0.0341364075200196</v>
+      </c>
+      <c r="E5">
+        <v>0.06488789007498311</v>
+      </c>
+      <c r="F5">
+        <v>2214</v>
+      </c>
+      <c r="G5">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>0.0258002425161464</v>
+      </c>
+      <c r="D6">
+        <v>0.0297498920040281</v>
+      </c>
+      <c r="E6">
+        <v>0.3859282107086426</v>
+      </c>
+      <c r="F6">
+        <v>1943</v>
+      </c>
+      <c r="G6">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>0.0442077948114511</v>
+      </c>
+      <c r="D7">
+        <v>0.0293328515590822</v>
+      </c>
+      <c r="E7">
+        <v>0.1319478291150173</v>
+      </c>
+      <c r="F7">
+        <v>2075</v>
+      </c>
+      <c r="G7">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2">
-        <v>0.0480744591291271</v>
-      </c>
-      <c r="E2">
-        <v>0.0328988971704961</v>
-      </c>
-      <c r="F2">
-        <v>0.1441026766242277</v>
-      </c>
-      <c r="H2">
-        <v>-0.0060394112044669</v>
-      </c>
-      <c r="I2">
-        <v>0.1021883294627213</v>
-      </c>
-      <c r="J2">
-        <v>0.9</v>
-      </c>
-      <c r="K2">
-        <v>2080</v>
-      </c>
-      <c r="L2">
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>0.0463944535755606</v>
+      </c>
+      <c r="D8">
+        <v>0.0316957545994971</v>
+      </c>
+      <c r="E8">
+        <v>0.1434548772958428</v>
+      </c>
+      <c r="F8">
+        <v>1806</v>
+      </c>
+      <c r="G8">
         <v>141</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3">
-        <v>0.0476889951911409</v>
-      </c>
-      <c r="E3">
-        <v>0.0326653359814922</v>
-      </c>
-      <c r="F3">
-        <v>0.1444865908404664</v>
-      </c>
-      <c r="H3">
-        <v>-0.0060407011736049</v>
-      </c>
-      <c r="I3">
-        <v>0.1014186915558868</v>
-      </c>
-      <c r="J3">
-        <v>0.9</v>
-      </c>
-      <c r="K3">
-        <v>1941</v>
-      </c>
-      <c r="L3">
-        <v>141</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S3" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
